--- a/Result/profitability/1570.xlsx
+++ b/Result/profitability/1570.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.04</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2575</v>
+        <v>0.2075</v>
       </c>
       <c r="N2" t="n">
-        <v>25.45625</v>
+        <v>24.0425</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.19</v>
       </c>
       <c r="M3" t="n">
-        <v>0.145</v>
+        <v>0.12125</v>
       </c>
       <c r="N3" t="n">
-        <v>22.76375</v>
+        <v>22.52625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>0.16</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1025</v>
+        <v>0.08750000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>22.2475</v>
+        <v>20.7075</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.31</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.115</v>
+        <v>-0.07625000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>19.84875</v>
+        <v>19.22</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.12375</v>
+        <v>-0.1125</v>
       </c>
       <c r="N6" t="n">
-        <v>17.7375</v>
+        <v>18.42125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-2.46</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.45875</v>
+        <v>-0.41125</v>
       </c>
       <c r="N7" t="n">
-        <v>15.76375</v>
+        <v>15.75375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.23</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.47875</v>
+        <v>-0.46875</v>
       </c>
       <c r="N8" t="n">
-        <v>14.76625</v>
+        <v>14.66</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>-0.33</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.54875</v>
+        <v>-0.5487500000000001</v>
       </c>
       <c r="N9" t="n">
         <v>12.14875</v>
@@ -9828,6 +9828,135 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1570</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>169</v>
+      </c>
+      <c r="D75" t="n">
+        <v>132</v>
+      </c>
+      <c r="E75" t="n">
+        <v>37</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="G75" t="n">
+        <v>19</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.07%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>20</v>
+      </c>
+      <c r="K75" t="n">
+        <v>16</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>25.0125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.07999999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3478260869565217</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.8499999999999979</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03759398496240596</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.029999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1877566256065696</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
